--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31998-2026 artfynd.xlsx
+++ b/artfynd/A 31998-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791513</v>
       </c>
       <c r="B2" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
